--- a/backend/data/rule_sets/change_general_1783407559_4bc7e0/source.xlsx
+++ b/backend/data/rule_sets/change_general_1783407559_4bc7e0/source.xlsx
@@ -2700,7 +2700,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"财产来源","op":"contains_any","values":["财产权"]},"target":{"field":"产品基本信息.是否信托受益权转让","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.财产来源","op":"contains","value":"财产权"},"target":{"field":"产品基本信息.是否信托受益权转让","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2736,7 +2736,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否信托受益权转让","op":"equals","value":"拆分转让"},"target":{"field":"产品基本信息.发行、转让场所","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.是否信托受益权转让","op":"contains_any","values":["拆分转让","整体转让"]},"target":{"field":"产品基本信息.发行、转让场所","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3024,7 +3028,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"发行、转让场所","op":"equals","value":"其他"},"target":{"field":"产品基本信息.发行、转让场所补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.发行、转让场所","op":"equals","value":"其他"},"target":{"field":"产品基本信息.发行、转让场所补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3214,7 +3222,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3753,7 +3765,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"开放频度","op":"equals","value":"其他"},"target":{"field":"产品基本信息.开放频度补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.开放频度","op":"equals","value":"其他"},"target":{"field":"产品基本信息.开放频度补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3789,7 +3801,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3944,7 +3960,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"产品基本信息.是否为结构化信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"产品基本信息.是否为结构化信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3980,7 +3996,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4134,7 +4154,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否为结构化信托","op":"equals","value":"是"},"target":{"field":"产品基本信息.约定优先劣后受益权比例","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.是否为结构化信托","op":"equals","value":"是"},"target":{"field":"产品基本信息.约定优先劣后受益权比例","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4170,7 +4190,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4514,7 +4538,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"logic":"AND","conditions":[{"field":"信托业务分类","op":"equals","value":"资产管理信托"},{"field":"项目运作模式","op":"equals","value":"封闭式"}]},"target":{"field":"产品基本信息.是否分期募集放款","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},{"field":"产品基本信息.项目运作模式","op":"equals","value":"封闭式"}]},"target":{"field":"产品基本信息.是否分期募集放款","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4550,7 +4574,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -5180,7 +5208,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"业务分类信息.资产管理信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"业务分类信息.资产管理信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5216,7 +5244,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5375,7 +5407,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类1","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类1","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -5411,7 +5443,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5574,7 +5610,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类2","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类2","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -5610,7 +5646,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5766,7 +5806,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.公益慈善信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.公益慈善信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5802,7 +5842,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5957,7 +6001,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.是否在民政部门备案","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.是否在民政部门备案","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5993,7 +6037,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -6147,7 +6195,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.待整改原因","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.待整改原因","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6183,7 +6231,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -6337,7 +6389,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.整改计划","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.整改计划","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -6373,7 +6425,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6527,7 +6583,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.计划完成整改时间","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.计划完成整改时间","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -6563,7 +6619,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6718,7 +6778,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否以管理契约型私募基金形式开展资产管理信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否以管理契约型私募基金形式开展资产管理信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6754,7 +6814,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6909,7 +6973,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否金融通道业务","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否金融通道业务","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6945,7 +7009,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7100,7 +7168,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否为融资方服务的私募投行业务","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否为融资方服务的私募投行业务","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -7136,7 +7204,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7291,7 +7363,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.是否参与资金募集","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.是否参与资金募集","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -7327,7 +7399,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7482,7 +7558,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否满足非公开发行要求","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否满足非公开发行要求","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -7518,7 +7594,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7766,7 +7846,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否互联网贷款","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否互联网贷款","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -7802,7 +7882,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7961,7 +8045,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否互联网贷款","op":"equals","value":"是"},"target":{"field":"产品特征.业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品特征.是否互联网贷款","op":"equals","value":"是"},"target":{"field":"产品特征.业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7997,7 +8081,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8152,7 +8240,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否证券投资类信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否证券投资类信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -8188,7 +8276,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8343,7 +8435,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否受托境外理财信托（QDII）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否受托境外理财信托（QDII）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -8379,7 +8471,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8725,7 +8821,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否绿色信托","op":"equals","value":"是"},"target":{"field":"产品特征.绿色信托业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品特征.是否绿色信托","op":"equals","value":"是"},"target":{"field":"产品特征.绿色信托业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -8761,7 +8857,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8915,7 +9015,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否城市更新","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否城市更新","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -8951,7 +9051,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -9482,7 +9586,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否资产证券双SPV结构下的资产层信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否资产证券双SPV结构下的资产层信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -9518,7 +9622,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -13123,7 +13231,7 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集起始日期","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集起始日期","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -13159,7 +13267,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -13313,7 +13425,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集结束日期","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集结束日期","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -13349,7 +13461,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -13503,7 +13619,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"期限类型","op":"equals","value":"固定期限"},"target":{"field":"初始信托规模.信托产品期限","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始信托规模.期限类型","op":"equals","value":"固定期限"},"target":{"field":"初始信托规模.信托产品期限","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -13539,7 +13655,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -15884,7 +16004,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -15920,7 +16040,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -16081,7 +16205,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -16117,7 +16241,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -16271,7 +16399,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -16307,7 +16435,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -16462,7 +16594,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -16498,7 +16630,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -16652,7 +16788,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"contains_any","values":["非金融企业","金融机构（实体）"]},"target":{"field":"初始委托人及其财产信息.委托人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"contains_any","values":["非金融企业","金融机构（实体"]},"target":{"field":"初始委托人及其财产信息.委托人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -16688,7 +16824,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -17033,7 +17173,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托资产类型","op":"contains_any","values":["其他"]},"target":{"field":"初始委托人及其财产信息.委托资产类型补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托资产类型","op":"contains","value":"其他"},"target":{"field":"初始委托人及其财产信息.委托资产类型补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -17069,7 +17209,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -18922,7 +19066,7 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -18958,7 +19102,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -19115,7 +19263,7 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
@@ -19151,7 +19299,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -19305,7 +19457,7 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -19341,7 +19493,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -19496,7 +19652,7 @@
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -19532,7 +19688,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -19687,7 +19847,7 @@
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"contains_any","values":["非金融企业","金融机构（实体）"]},"target":{"field":"初始受益权信息.受益人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"contains_any","values":["非金融企业","金融机构（实体"]},"target":{"field":"初始受益权信息.受益人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
@@ -19723,7 +19883,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -20156,7 +20320,7 @@
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"运作模式","op":"equals","value":"封闭式净值型"},"target":{"field":"初始受益权信息.单位净值","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"运作模式","op":"contains_any","values":["封闭式净值型","开放式净值型"]},"target":{"field":"初始受益权信息.单位净值","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
@@ -20192,7 +20356,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -21091,7 +21259,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（下限）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（下限）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr">
@@ -21127,7 +21295,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -21281,7 +21453,7 @@
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（上限）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（上限）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N219" s="2" t="inlineStr">
@@ -21317,7 +21489,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
